--- a/outputs/tables/appendix_e_matched_window.xlsx
+++ b/outputs/tables/appendix_e_matched_window.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968</v>
+        <v>0.972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>0.958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.897</v>
+        <v>0.891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.956</v>
+        <v>0.961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.898</v>
+        <v>0.896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.883</v>
+        <v>0.884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.965</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.994</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.695</v>
+        <v>0.721</v>
       </c>
       <c r="D5" t="n">
-        <v>0.644</v>
+        <v>0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>0.643</v>
+        <v>0.574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.708</v>
+        <v>0.68</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.487</v>
+        <v>0.398</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.769</v>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.626</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.609</v>
       </c>
       <c r="J6" t="n">
-        <v>0.657</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +642,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.477</v>
+        <v>0.733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.779</v>
+        <v>0.709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.636</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="8">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.876</v>
+        <v>0.895</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.787</v>
       </c>
       <c r="F8" t="n">
-        <v>0.755</v>
+        <v>0.744</v>
       </c>
       <c r="G8" t="n">
-        <v>0.921</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.924</v>
+        <v>0.925</v>
       </c>
       <c r="I8" t="n">
-        <v>0.868</v>
+        <v>0.877</v>
       </c>
       <c r="J8" t="n">
-        <v>0.858</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.891</v>
+        <v>0.921</v>
       </c>
       <c r="E9" t="n">
-        <v>0.708</v>
+        <v>0.855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.877</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911</v>
+        <v>0.914</v>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>0.974</v>
       </c>
       <c r="I9" t="n">
-        <v>0.894</v>
+        <v>0.899</v>
       </c>
       <c r="J9" t="n">
-        <v>0.971</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="10">
@@ -740,28 +740,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.835</v>
       </c>
       <c r="D10" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.869</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.799</v>
-      </c>
       <c r="F10" t="n">
-        <v>0.864</v>
+        <v>0.866</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.971</v>
+        <v>0.986</v>
       </c>
       <c r="I10" t="n">
-        <v>0.916</v>
+        <v>0.927</v>
       </c>
       <c r="J10" t="n">
-        <v>0.958</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="11">
@@ -779,25 +779,25 @@
         <v>0.859</v>
       </c>
       <c r="D11" t="n">
-        <v>0.797</v>
+        <v>0.825</v>
       </c>
       <c r="E11" t="n">
-        <v>0.802</v>
+        <v>0.728</v>
       </c>
       <c r="F11" t="n">
-        <v>0.741</v>
+        <v>0.725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845</v>
+        <v>0.841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.859</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="12">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.793</v>
+        <v>0.679</v>
       </c>
       <c r="D12" t="n">
-        <v>0.946</v>
+        <v>0.915</v>
       </c>
       <c r="E12" t="n">
-        <v>0.626</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>0.856</v>
+        <v>0.862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.896</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.73</v>
+        <v>0.781</v>
       </c>
       <c r="D13" t="n">
-        <v>0.806</v>
+        <v>0.832</v>
       </c>
       <c r="E13" t="n">
-        <v>0.739</v>
+        <v>0.613</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.805</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.914</v>
       </c>
       <c r="I13" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="J13" t="n">
-        <v>0.899</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="14">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.854</v>
+        <v>0.881</v>
       </c>
       <c r="D14" t="n">
-        <v>0.806</v>
+        <v>0.82</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.896</v>
+        <v>0.882</v>
       </c>
       <c r="H14" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="J14" t="n">
-        <v>0.849</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="15">
@@ -905,28 +905,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.715</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="E15" t="n">
-        <v>0.631</v>
+        <v>0.501</v>
       </c>
       <c r="F15" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.819</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.893</v>
+        <v>0.881</v>
       </c>
       <c r="J15" t="n">
-        <v>0.859</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="16">
@@ -936,28 +936,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.891</v>
+        <v>0.843</v>
       </c>
       <c r="E16" t="n">
-        <v>0.504</v>
+        <v>0.66</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.911</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.928</v>
+        <v>0.901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.863</v>
+        <v>0.888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="17">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.829</v>
+        <v>0.785</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.775</v>
+        <v>0.715</v>
       </c>
       <c r="F17" t="n">
-        <v>0.707</v>
+        <v>0.712</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>0.837</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.823</v>
       </c>
       <c r="J17" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="18">
@@ -1003,28 +1003,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.804</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.773</v>
       </c>
       <c r="E18" t="n">
-        <v>0.636</v>
+        <v>0.649</v>
       </c>
       <c r="F18" t="n">
-        <v>0.668</v>
+        <v>0.759</v>
       </c>
       <c r="G18" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="I18" t="n">
-        <v>0.91</v>
+        <v>0.917</v>
       </c>
       <c r="J18" t="n">
-        <v>0.873</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="19">
@@ -1034,28 +1034,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.742</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="E19" t="n">
-        <v>0.539</v>
+        <v>0.549</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.714</v>
       </c>
       <c r="G19" t="n">
-        <v>0.953</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.016</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="3">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.897</v>
+        <v>0.891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.187</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1387,16 +1387,16 @@
         <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.898</v>
+        <v>0.896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.883</v>
+        <v>0.884</v>
       </c>
       <c r="G4" t="n">
         <v>0.145</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.015</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="5">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.613</v>
+        <v>0.652</v>
       </c>
       <c r="E5" t="n">
-        <v>0.695</v>
+        <v>0.721</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643</v>
+        <v>0.574</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029</v>
+        <v>-0.078</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.052</v>
+        <v>-0.147</v>
       </c>
     </row>
     <row r="6">
@@ -1448,19 +1448,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="E6" t="n">
-        <v>0.487</v>
+        <v>0.398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63</v>
+        <v>0.529</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.143</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="7">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.474</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-0.107</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003</v>
+        <v>-0.176</v>
       </c>
     </row>
     <row r="8">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.745</v>
+        <v>0.767</v>
       </c>
       <c r="E8" t="n">
-        <v>0.876</v>
+        <v>0.895</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.787</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="9">
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="E9" t="n">
-        <v>0.848</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.708</v>
+        <v>0.855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.024</v>
+        <v>0.214</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="10">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.646</v>
+        <v>0.645</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.835</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.869</v>
       </c>
       <c r="G10" t="n">
-        <v>0.154</v>
+        <v>0.225</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="11">
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="E11" t="n">
         <v>0.859</v>
       </c>
       <c r="F11" t="n">
-        <v>0.802</v>
+        <v>0.728</v>
       </c>
       <c r="G11" t="n">
-        <v>0.054</v>
+        <v>-0.021</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.057</v>
+        <v>-0.131</v>
       </c>
     </row>
     <row r="12">
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.641</v>
       </c>
       <c r="E12" t="n">
-        <v>0.793</v>
+        <v>0.679</v>
       </c>
       <c r="F12" t="n">
-        <v>0.626</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.082</v>
+        <v>-0.075</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.167</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="13">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.677</v>
+        <v>0.713</v>
       </c>
       <c r="E13" t="n">
-        <v>0.73</v>
+        <v>0.781</v>
       </c>
       <c r="F13" t="n">
-        <v>0.739</v>
+        <v>0.613</v>
       </c>
       <c r="G13" t="n">
-        <v>0.062</v>
+        <v>-0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="14">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.747</v>
+        <v>0.757</v>
       </c>
       <c r="E14" t="n">
-        <v>0.854</v>
+        <v>0.881</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062</v>
+        <v>-0.033</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.045</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="15">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.657</v>
+        <v>0.697</v>
       </c>
       <c r="E15" t="n">
-        <v>0.715</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.631</v>
+        <v>0.501</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-0.196</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.313</v>
       </c>
     </row>
     <row r="16">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="F16" t="n">
-        <v>0.504</v>
+        <v>0.66</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.18</v>
+        <v>-0.02</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.312</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>0.701</v>
       </c>
       <c r="E17" t="n">
-        <v>0.829</v>
+        <v>0.785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.775</v>
+        <v>0.715</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031</v>
+        <v>0.014</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.054</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.582</v>
+        <v>0.613</v>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.636</v>
+        <v>0.649</v>
       </c>
       <c r="G18" t="n">
-        <v>0.054</v>
+        <v>0.036</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124</v>
+        <v>-0.154</v>
       </c>
     </row>
     <row r="19">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="E19" t="n">
-        <v>0.742</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539</v>
+        <v>0.549</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.027</v>
+        <v>0.007</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.203</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="20">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.869</v>
+        <v>0.862</v>
       </c>
       <c r="E20" t="n">
-        <v>0.968</v>
+        <v>0.972</v>
       </c>
       <c r="F20" t="n">
-        <v>0.969</v>
+        <v>0.958</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="21">
@@ -1928,19 +1928,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.027</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="22">
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136</v>
+        <v>0.116</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="23">
@@ -1992,19 +1992,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.602</v>
       </c>
       <c r="E23" t="n">
-        <v>0.644</v>
+        <v>0.66</v>
       </c>
       <c r="F23" t="n">
-        <v>0.624</v>
+        <v>0.6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="24">
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.744</v>
+        <v>0.792</v>
       </c>
       <c r="E24" t="n">
-        <v>0.695</v>
+        <v>0.769</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.055</v>
+        <v>-0.201</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.007</v>
+        <v>-0.177</v>
       </c>
     </row>
     <row r="25">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.739</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.709</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>-0.108</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.096</v>
       </c>
     </row>
     <row r="26">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.717</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.832</v>
       </c>
       <c r="F26" t="n">
-        <v>0.755</v>
+        <v>0.744</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.056</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.701</v>
+        <v>0.742</v>
       </c>
       <c r="E27" t="n">
-        <v>0.891</v>
+        <v>0.921</v>
       </c>
       <c r="F27" t="n">
-        <v>0.883</v>
+        <v>0.877</v>
       </c>
       <c r="G27" t="n">
-        <v>0.182</v>
+        <v>0.135</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.044</v>
       </c>
     </row>
     <row r="28">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.773</v>
       </c>
       <c r="E28" t="n">
-        <v>0.869</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.864</v>
+        <v>0.866</v>
       </c>
       <c r="G28" t="n">
-        <v>0.136</v>
+        <v>0.093</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.681</v>
+        <v>0.712</v>
       </c>
       <c r="E29" t="n">
-        <v>0.797</v>
+        <v>0.825</v>
       </c>
       <c r="F29" t="n">
-        <v>0.741</v>
+        <v>0.725</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.056</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="30">
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="E30" t="n">
-        <v>0.946</v>
+        <v>0.915</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.106</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="31">
@@ -2248,19 +2248,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.729</v>
+        <v>0.751</v>
       </c>
       <c r="E31" t="n">
-        <v>0.806</v>
+        <v>0.832</v>
       </c>
       <c r="F31" t="n">
-        <v>0.825</v>
+        <v>0.805</v>
       </c>
       <c r="G31" t="n">
-        <v>0.097</v>
+        <v>0.055</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="32">
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="E32" t="n">
-        <v>0.806</v>
+        <v>0.82</v>
       </c>
       <c r="F32" t="n">
-        <v>0.742</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.049</v>
+        <v>-0.02</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.129</v>
       </c>
     </row>
     <row r="33">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.756</v>
+        <v>0.741</v>
       </c>
       <c r="E33" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="F33" t="n">
-        <v>0.819</v>
+        <v>0.634</v>
       </c>
       <c r="G33" t="n">
-        <v>0.063</v>
+        <v>-0.107</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.015</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="34">
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.758</v>
       </c>
       <c r="E34" t="n">
-        <v>0.891</v>
+        <v>0.843</v>
       </c>
       <c r="F34" t="n">
-        <v>0.799</v>
+        <v>0.551</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.018</v>
+        <v>-0.206</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.093</v>
+        <v>-0.292</v>
       </c>
     </row>
     <row r="35">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="E35" t="n">
-        <v>0.678</v>
+        <v>0.757</v>
       </c>
       <c r="F35" t="n">
-        <v>0.707</v>
+        <v>0.712</v>
       </c>
       <c r="G35" t="n">
-        <v>0.097</v>
+        <v>0.031</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="36">
@@ -2408,19 +2408,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.603</v>
       </c>
       <c r="E36" t="n">
-        <v>0.756</v>
+        <v>0.773</v>
       </c>
       <c r="F36" t="n">
-        <v>0.668</v>
+        <v>0.759</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.155</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="37">
@@ -2440,19 +2440,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.641</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="F37" t="n">
-        <v>0.668</v>
+        <v>0.714</v>
       </c>
       <c r="G37" t="n">
-        <v>0.068</v>
+        <v>0.073</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.145</v>
+        <v>-0.132</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/appendix_e_matched_window.xlsx
+++ b/outputs/tables/appendix_e_matched_window.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>0.958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.897</v>
+        <v>0.871</v>
       </c>
       <c r="D3" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.956</v>
+        <v>0.961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.883</v>
+        <v>0.884</v>
       </c>
       <c r="F4" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.965</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.994</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.695</v>
+        <v>0.73</v>
       </c>
       <c r="D5" t="n">
-        <v>0.644</v>
+        <v>0.672</v>
       </c>
       <c r="E5" t="n">
-        <v>0.643</v>
+        <v>0.573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>0.739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.708</v>
+        <v>0.681</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.487</v>
+        <v>0.458</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.747</v>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.709</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.638</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.551</v>
       </c>
       <c r="J6" t="n">
-        <v>0.657</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +642,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.477</v>
+        <v>0.713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.637</v>
       </c>
       <c r="F7" t="n">
-        <v>0.779</v>
+        <v>0.591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.659</v>
+        <v>0.638</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.609</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.876</v>
+        <v>0.854</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.838</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="F8" t="n">
-        <v>0.755</v>
+        <v>0.714</v>
       </c>
       <c r="G8" t="n">
-        <v>0.921</v>
+        <v>0.915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.924</v>
+        <v>0.917</v>
       </c>
       <c r="I8" t="n">
-        <v>0.868</v>
+        <v>0.877</v>
       </c>
       <c r="J8" t="n">
-        <v>0.858</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.858</v>
       </c>
       <c r="D9" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="E9" t="n">
-        <v>0.708</v>
+        <v>0.907</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.849</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911</v>
+        <v>0.897</v>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>0.979</v>
       </c>
       <c r="I9" t="n">
-        <v>0.894</v>
+        <v>0.867</v>
       </c>
       <c r="J9" t="n">
-        <v>0.971</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -740,28 +740,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="D10" t="n">
-        <v>0.869</v>
+        <v>0.96</v>
       </c>
       <c r="E10" t="n">
-        <v>0.799</v>
+        <v>0.92</v>
       </c>
       <c r="F10" t="n">
-        <v>0.864</v>
+        <v>0.881</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>0.948</v>
       </c>
       <c r="H10" t="n">
-        <v>0.971</v>
+        <v>0.985</v>
       </c>
       <c r="I10" t="n">
-        <v>0.916</v>
+        <v>0.925</v>
       </c>
       <c r="J10" t="n">
-        <v>0.958</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="11">
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.859</v>
+        <v>0.834</v>
       </c>
       <c r="D11" t="n">
-        <v>0.797</v>
+        <v>0.805</v>
       </c>
       <c r="E11" t="n">
-        <v>0.802</v>
+        <v>0.728</v>
       </c>
       <c r="F11" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="G11" t="n">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845</v>
+        <v>0.841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.859</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="12">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.793</v>
+        <v>0.724</v>
       </c>
       <c r="D12" t="n">
-        <v>0.946</v>
+        <v>0.926</v>
       </c>
       <c r="E12" t="n">
-        <v>0.626</v>
+        <v>0.599</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>0.856</v>
+        <v>0.862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.896</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.73</v>
+        <v>0.775</v>
       </c>
       <c r="D13" t="n">
-        <v>0.806</v>
+        <v>0.883</v>
       </c>
       <c r="E13" t="n">
-        <v>0.739</v>
+        <v>0.68</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.914</v>
       </c>
       <c r="I13" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="J13" t="n">
-        <v>0.899</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="14">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.854</v>
+        <v>0.868</v>
       </c>
       <c r="D14" t="n">
-        <v>0.806</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742</v>
+        <v>0.735</v>
       </c>
       <c r="G14" t="n">
-        <v>0.896</v>
+        <v>0.882</v>
       </c>
       <c r="H14" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="J14" t="n">
-        <v>0.849</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="15">
@@ -905,28 +905,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.715</v>
+        <v>0.839</v>
       </c>
       <c r="D15" t="n">
-        <v>0.834</v>
+        <v>0.799</v>
       </c>
       <c r="E15" t="n">
-        <v>0.631</v>
+        <v>0.574</v>
       </c>
       <c r="F15" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.819</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.893</v>
+        <v>0.881</v>
       </c>
       <c r="J15" t="n">
-        <v>0.859</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="16">
@@ -936,28 +936,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="D16" t="n">
-        <v>0.891</v>
+        <v>0.841</v>
       </c>
       <c r="E16" t="n">
-        <v>0.504</v>
+        <v>0.622</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.728</v>
       </c>
       <c r="G16" t="n">
-        <v>0.911</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.928</v>
+        <v>0.901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.863</v>
+        <v>0.888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="17">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.829</v>
+        <v>0.731</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.769</v>
       </c>
       <c r="E17" t="n">
-        <v>0.775</v>
+        <v>0.677</v>
       </c>
       <c r="F17" t="n">
-        <v>0.707</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.846</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>0.843</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.789</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="18">
@@ -1003,28 +1003,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.707</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.833</v>
       </c>
       <c r="E18" t="n">
-        <v>0.636</v>
+        <v>0.497</v>
       </c>
       <c r="F18" t="n">
-        <v>0.668</v>
+        <v>0.77</v>
       </c>
       <c r="G18" t="n">
-        <v>0.927</v>
+        <v>0.918</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.916</v>
       </c>
       <c r="I18" t="n">
-        <v>0.91</v>
+        <v>0.926</v>
       </c>
       <c r="J18" t="n">
-        <v>0.873</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="19">
@@ -1034,28 +1034,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.742</v>
+        <v>0.766</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="E19" t="n">
-        <v>0.539</v>
+        <v>0.633</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.735</v>
       </c>
       <c r="G19" t="n">
-        <v>0.953</v>
+        <v>0.927</v>
       </c>
       <c r="H19" t="n">
-        <v>0.949</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.961</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.016</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="3">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.897</v>
+        <v>0.871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.187</v>
+        <v>0.153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="4">
@@ -1387,16 +1387,16 @@
         <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.883</v>
+        <v>0.884</v>
       </c>
       <c r="G4" t="n">
         <v>0.145</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.015</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="5">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.613</v>
+        <v>0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>0.695</v>
+        <v>0.73</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643</v>
+        <v>0.573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.052</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="6">
@@ -1448,16 +1448,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.487</v>
+        <v>0.458</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63</v>
+        <v>0.602</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.043</v>
       </c>
       <c r="H6" t="n">
         <v>0.143</v>
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.713</v>
       </c>
       <c r="F7" t="n">
-        <v>0.474</v>
+        <v>0.637</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="8">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="E8" t="n">
-        <v>0.876</v>
+        <v>0.854</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="9">
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.661</v>
       </c>
       <c r="E9" t="n">
-        <v>0.848</v>
+        <v>0.858</v>
       </c>
       <c r="F9" t="n">
-        <v>0.708</v>
+        <v>0.907</v>
       </c>
       <c r="G9" t="n">
-        <v>0.024</v>
+        <v>0.246</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="10">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.646</v>
+        <v>0.678</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.92</v>
       </c>
       <c r="G10" t="n">
-        <v>0.154</v>
+        <v>0.242</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="11">
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.748</v>
+        <v>0.732</v>
       </c>
       <c r="E11" t="n">
-        <v>0.859</v>
+        <v>0.834</v>
       </c>
       <c r="F11" t="n">
-        <v>0.802</v>
+        <v>0.728</v>
       </c>
       <c r="G11" t="n">
-        <v>0.054</v>
+        <v>-0.005</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.057</v>
+        <v>-0.106</v>
       </c>
     </row>
     <row r="12">
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="E12" t="n">
-        <v>0.793</v>
+        <v>0.724</v>
       </c>
       <c r="F12" t="n">
-        <v>0.626</v>
+        <v>0.599</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.082</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.167</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="13">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.677</v>
+        <v>0.709</v>
       </c>
       <c r="E13" t="n">
-        <v>0.73</v>
+        <v>0.775</v>
       </c>
       <c r="F13" t="n">
-        <v>0.739</v>
+        <v>0.68</v>
       </c>
       <c r="G13" t="n">
-        <v>0.062</v>
+        <v>-0.029</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="14">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="E14" t="n">
-        <v>0.854</v>
+        <v>0.868</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062</v>
+        <v>-0.017</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.045</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="15">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.657</v>
+        <v>0.714</v>
       </c>
       <c r="E15" t="n">
-        <v>0.715</v>
+        <v>0.839</v>
       </c>
       <c r="F15" t="n">
-        <v>0.631</v>
+        <v>0.574</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-0.14</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="16">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="F16" t="n">
-        <v>0.504</v>
+        <v>0.622</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.18</v>
+        <v>-0.066</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.312</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="17">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>0.665</v>
       </c>
       <c r="E17" t="n">
-        <v>0.829</v>
+        <v>0.731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.775</v>
+        <v>0.677</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.054</v>
+        <v>-0.055</v>
       </c>
     </row>
     <row r="18">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.582</v>
+        <v>0.547</v>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.707</v>
       </c>
       <c r="F18" t="n">
-        <v>0.636</v>
+        <v>0.497</v>
       </c>
       <c r="G18" t="n">
-        <v>0.054</v>
+        <v>-0.05</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="19">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.594</v>
       </c>
       <c r="E19" t="n">
-        <v>0.742</v>
+        <v>0.766</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539</v>
+        <v>0.633</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.027</v>
+        <v>0.039</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.203</v>
+        <v>-0.133</v>
       </c>
     </row>
     <row r="20">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.869</v>
+        <v>0.865</v>
       </c>
       <c r="E20" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.969</v>
+        <v>0.958</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.092</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1928,19 +1928,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.027</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="22">
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>0.902</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.03</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="23">
@@ -1992,19 +1992,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.608</v>
       </c>
       <c r="E23" t="n">
-        <v>0.644</v>
+        <v>0.672</v>
       </c>
       <c r="F23" t="n">
-        <v>0.624</v>
+        <v>0.608</v>
       </c>
       <c r="G23" t="n">
-        <v>0.015</v>
+        <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="24">
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.744</v>
+        <v>0.777</v>
       </c>
       <c r="E24" t="n">
-        <v>0.695</v>
+        <v>0.747</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.709</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.055</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.007</v>
+        <v>-0.038</v>
       </c>
     </row>
     <row r="25">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.739</v>
+        <v>0.792</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.768</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.591</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>-0.2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.177</v>
       </c>
     </row>
     <row r="26">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.717</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.838</v>
       </c>
       <c r="F26" t="n">
-        <v>0.755</v>
+        <v>0.714</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.002</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.056</v>
+        <v>-0.124</v>
       </c>
     </row>
     <row r="27">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.701</v>
+        <v>0.736</v>
       </c>
       <c r="E27" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="F27" t="n">
-        <v>0.883</v>
+        <v>0.849</v>
       </c>
       <c r="G27" t="n">
-        <v>0.182</v>
+        <v>0.113</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="28">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.796</v>
       </c>
       <c r="E28" t="n">
-        <v>0.869</v>
+        <v>0.96</v>
       </c>
       <c r="F28" t="n">
-        <v>0.864</v>
+        <v>0.881</v>
       </c>
       <c r="G28" t="n">
-        <v>0.136</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.079</v>
       </c>
     </row>
     <row r="29">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.681</v>
+        <v>0.699</v>
       </c>
       <c r="E29" t="n">
-        <v>0.797</v>
+        <v>0.805</v>
       </c>
       <c r="F29" t="n">
-        <v>0.741</v>
+        <v>0.736</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06</v>
+        <v>0.038</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.056</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="30">
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.946</v>
+        <v>0.926</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.799</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022</v>
+        <v>-0.013</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.106</v>
+        <v>-0.126</v>
       </c>
     </row>
     <row r="31">
@@ -2248,19 +2248,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.729</v>
+        <v>0.785</v>
       </c>
       <c r="E31" t="n">
-        <v>0.806</v>
+        <v>0.883</v>
       </c>
       <c r="F31" t="n">
-        <v>0.825</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.097</v>
+        <v>0.025</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="32">
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="E32" t="n">
-        <v>0.806</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.742</v>
+        <v>0.735</v>
       </c>
       <c r="G32" t="n">
-        <v>0.049</v>
+        <v>0.032</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="33">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.756</v>
+        <v>0.718</v>
       </c>
       <c r="E33" t="n">
-        <v>0.834</v>
+        <v>0.799</v>
       </c>
       <c r="F33" t="n">
-        <v>0.819</v>
+        <v>0.798</v>
       </c>
       <c r="G33" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.015</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="34">
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.756</v>
       </c>
       <c r="E34" t="n">
-        <v>0.891</v>
+        <v>0.841</v>
       </c>
       <c r="F34" t="n">
-        <v>0.799</v>
+        <v>0.728</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.018</v>
+        <v>-0.028</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.093</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="35">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.61</v>
+        <v>0.674</v>
       </c>
       <c r="E35" t="n">
-        <v>0.678</v>
+        <v>0.769</v>
       </c>
       <c r="F35" t="n">
-        <v>0.707</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.097</v>
+        <v>0.008</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2408,19 +2408,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="E36" t="n">
-        <v>0.756</v>
+        <v>0.833</v>
       </c>
       <c r="F36" t="n">
-        <v>0.668</v>
+        <v>0.77</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.13</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="37">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F37" t="n">
-        <v>0.668</v>
+        <v>0.735</v>
       </c>
       <c r="G37" t="n">
-        <v>0.068</v>
+        <v>0.064</v>
       </c>
       <c r="H37" t="n">
         <v>-0.145</v>

--- a/outputs/tables/appendix_e_matched_window.xlsx
+++ b/outputs/tables/appendix_e_matched_window.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.897</v>
+        <v>0.866</v>
       </c>
       <c r="D3" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.956</v>
+        <v>0.961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
       <c r="F4" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.965</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.994</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.695</v>
+        <v>0.719</v>
       </c>
       <c r="D5" t="n">
-        <v>0.644</v>
+        <v>0.665</v>
       </c>
       <c r="E5" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>0.752</v>
       </c>
       <c r="I5" t="n">
-        <v>0.708</v>
+        <v>0.677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.487</v>
+        <v>0.419</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.771</v>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.605</v>
       </c>
       <c r="J6" t="n">
-        <v>0.657</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +642,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.477</v>
+        <v>0.733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.779</v>
+        <v>0.649</v>
       </c>
       <c r="G7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="8">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.755</v>
+        <v>0.722</v>
       </c>
       <c r="G8" t="n">
-        <v>0.921</v>
+        <v>0.913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.924</v>
+        <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>0.868</v>
+        <v>0.865</v>
       </c>
       <c r="J8" t="n">
-        <v>0.858</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.853</v>
       </c>
       <c r="D9" t="n">
-        <v>0.891</v>
+        <v>0.903</v>
       </c>
       <c r="E9" t="n">
-        <v>0.708</v>
+        <v>0.853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911</v>
+        <v>0.901</v>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>0.981</v>
       </c>
       <c r="I9" t="n">
-        <v>0.894</v>
+        <v>0.898</v>
       </c>
       <c r="J9" t="n">
-        <v>0.971</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="10">
@@ -740,28 +740,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="D10" t="n">
-        <v>0.869</v>
+        <v>0.944</v>
       </c>
       <c r="E10" t="n">
-        <v>0.799</v>
+        <v>0.884</v>
       </c>
       <c r="F10" t="n">
-        <v>0.864</v>
+        <v>0.898</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>0.965</v>
       </c>
       <c r="H10" t="n">
-        <v>0.971</v>
+        <v>0.975</v>
       </c>
       <c r="I10" t="n">
-        <v>0.916</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.958</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="11">
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.859</v>
+        <v>0.854</v>
       </c>
       <c r="D11" t="n">
-        <v>0.797</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.802</v>
+        <v>0.752</v>
       </c>
       <c r="F11" t="n">
-        <v>0.741</v>
+        <v>0.715</v>
       </c>
       <c r="G11" t="n">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845</v>
+        <v>0.841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.859</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="12">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.793</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.946</v>
+        <v>0.861</v>
       </c>
       <c r="E12" t="n">
-        <v>0.626</v>
+        <v>0.669</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="G12" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>0.856</v>
+        <v>0.862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.896</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.73</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.806</v>
+        <v>0.898</v>
       </c>
       <c r="E13" t="n">
-        <v>0.739</v>
+        <v>0.653</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.756</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.914</v>
       </c>
       <c r="I13" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="J13" t="n">
-        <v>0.899</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="14">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.854</v>
+        <v>0.863</v>
       </c>
       <c r="D14" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742</v>
+        <v>0.732</v>
       </c>
       <c r="G14" t="n">
-        <v>0.896</v>
+        <v>0.882</v>
       </c>
       <c r="H14" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="J14" t="n">
-        <v>0.849</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="15">
@@ -905,28 +905,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.715</v>
+        <v>0.823</v>
       </c>
       <c r="D15" t="n">
-        <v>0.834</v>
+        <v>0.887</v>
       </c>
       <c r="E15" t="n">
-        <v>0.631</v>
+        <v>0.577</v>
       </c>
       <c r="F15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.819</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.893</v>
+        <v>0.881</v>
       </c>
       <c r="J15" t="n">
-        <v>0.859</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="16">
@@ -936,28 +936,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="D16" t="n">
-        <v>0.891</v>
+        <v>0.835</v>
       </c>
       <c r="E16" t="n">
-        <v>0.504</v>
+        <v>0.666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.71</v>
       </c>
       <c r="G16" t="n">
-        <v>0.911</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.928</v>
+        <v>0.901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.863</v>
+        <v>0.888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="17">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.829</v>
+        <v>0.668</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.723</v>
       </c>
       <c r="E17" t="n">
-        <v>0.775</v>
+        <v>0.665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.707</v>
+        <v>0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.849</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>0.844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.789</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="18">
@@ -1003,28 +1003,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.897</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.828</v>
       </c>
       <c r="E18" t="n">
-        <v>0.636</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.668</v>
+        <v>0.646</v>
       </c>
       <c r="G18" t="n">
-        <v>0.927</v>
+        <v>0.925</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="I18" t="n">
-        <v>0.91</v>
+        <v>0.912</v>
       </c>
       <c r="J18" t="n">
-        <v>0.873</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="19">
@@ -1034,28 +1034,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.742</v>
+        <v>0.765</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.539</v>
+        <v>0.555</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.68</v>
       </c>
       <c r="G19" t="n">
-        <v>0.953</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.949</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.971</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.016</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="3">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.897</v>
+        <v>0.866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.187</v>
+        <v>0.156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1387,16 +1387,16 @@
         <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.883</v>
+        <v>0.886</v>
       </c>
       <c r="G4" t="n">
-        <v>0.145</v>
+        <v>0.147</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.015</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.613</v>
+        <v>0.653</v>
       </c>
       <c r="E5" t="n">
-        <v>0.695</v>
+        <v>0.719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029</v>
+        <v>-0.016</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.052</v>
+        <v>-0.083</v>
       </c>
     </row>
     <row r="6">
@@ -1448,19 +1448,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.534</v>
       </c>
       <c r="E6" t="n">
-        <v>0.487</v>
+        <v>0.419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63</v>
+        <v>0.538</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.143</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="7">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.53</v>
+        <v>0.664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.474</v>
+        <v>0.622</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-0.043</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="8">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.745</v>
+        <v>0.759</v>
       </c>
       <c r="E8" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06</v>
+        <v>-0.103</v>
       </c>
     </row>
     <row r="9">
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="E9" t="n">
-        <v>0.848</v>
+        <v>0.853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.708</v>
+        <v>0.853</v>
       </c>
       <c r="G9" t="n">
-        <v>0.024</v>
+        <v>0.181</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="10">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.646</v>
+        <v>0.681</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.884</v>
       </c>
       <c r="G10" t="n">
-        <v>0.154</v>
+        <v>0.203</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="11">
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="E11" t="n">
-        <v>0.859</v>
+        <v>0.854</v>
       </c>
       <c r="F11" t="n">
-        <v>0.802</v>
+        <v>0.752</v>
       </c>
       <c r="G11" t="n">
-        <v>0.054</v>
+        <v>0.007</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.057</v>
+        <v>-0.101</v>
       </c>
     </row>
     <row r="12">
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.647</v>
       </c>
       <c r="E12" t="n">
-        <v>0.793</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.626</v>
+        <v>0.669</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.082</v>
+        <v>0.023</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.167</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="13">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.677</v>
+        <v>0.648</v>
       </c>
       <c r="E13" t="n">
-        <v>0.73</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.739</v>
+        <v>0.653</v>
       </c>
       <c r="G13" t="n">
-        <v>0.062</v>
+        <v>0.005</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="14">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="E14" t="n">
-        <v>0.854</v>
+        <v>0.863</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062</v>
+        <v>-0.027</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.045</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="15">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.657</v>
+        <v>0.703</v>
       </c>
       <c r="E15" t="n">
-        <v>0.715</v>
+        <v>0.823</v>
       </c>
       <c r="F15" t="n">
-        <v>0.631</v>
+        <v>0.577</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-0.126</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.245</v>
       </c>
     </row>
     <row r="16">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="F16" t="n">
-        <v>0.504</v>
+        <v>0.666</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.18</v>
+        <v>-0.02</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.312</v>
+        <v>-0.103</v>
       </c>
     </row>
     <row r="17">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>0.626</v>
       </c>
       <c r="E17" t="n">
-        <v>0.829</v>
+        <v>0.668</v>
       </c>
       <c r="F17" t="n">
-        <v>0.775</v>
+        <v>0.665</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031</v>
+        <v>0.039</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.054</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="18">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.582</v>
+        <v>0.668</v>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.897</v>
       </c>
       <c r="F18" t="n">
-        <v>0.636</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.054</v>
+        <v>-0.105</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124</v>
+        <v>-0.334</v>
       </c>
     </row>
     <row r="19">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E19" t="n">
-        <v>0.742</v>
+        <v>0.765</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539</v>
+        <v>0.555</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.027</v>
+        <v>-0.025</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.203</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="20">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.869</v>
+        <v>0.865</v>
       </c>
       <c r="E20" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1928,19 +1928,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.027</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="22">
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="23">
@@ -1992,19 +1992,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.604</v>
       </c>
       <c r="E23" t="n">
-        <v>0.644</v>
+        <v>0.665</v>
       </c>
       <c r="F23" t="n">
-        <v>0.624</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.015</v>
+        <v>-0.047</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.108</v>
       </c>
     </row>
     <row r="24">
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.744</v>
+        <v>0.793</v>
       </c>
       <c r="E24" t="n">
-        <v>0.695</v>
+        <v>0.771</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.055</v>
+        <v>-0.198</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.007</v>
+        <v>-0.175</v>
       </c>
     </row>
     <row r="25">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.739</v>
+        <v>0.781</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.649</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>-0.133</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.104</v>
       </c>
     </row>
     <row r="26">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="F26" t="n">
-        <v>0.755</v>
+        <v>0.722</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.017</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.056</v>
+        <v>-0.143</v>
       </c>
     </row>
     <row r="27">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.701</v>
+        <v>0.755</v>
       </c>
       <c r="E27" t="n">
-        <v>0.891</v>
+        <v>0.903</v>
       </c>
       <c r="F27" t="n">
-        <v>0.883</v>
+        <v>0.805</v>
       </c>
       <c r="G27" t="n">
-        <v>0.182</v>
+        <v>0.05</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.098</v>
       </c>
     </row>
     <row r="28">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.746</v>
       </c>
       <c r="E28" t="n">
-        <v>0.869</v>
+        <v>0.944</v>
       </c>
       <c r="F28" t="n">
-        <v>0.864</v>
+        <v>0.898</v>
       </c>
       <c r="G28" t="n">
-        <v>0.136</v>
+        <v>0.152</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="29">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.681</v>
+        <v>0.705</v>
       </c>
       <c r="E29" t="n">
-        <v>0.797</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.741</v>
+        <v>0.715</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.056</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="30">
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="E30" t="n">
-        <v>0.946</v>
+        <v>0.861</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022</v>
+        <v>-0.02</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.106</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="31">
@@ -2248,19 +2248,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.729</v>
+        <v>0.795</v>
       </c>
       <c r="E31" t="n">
-        <v>0.806</v>
+        <v>0.898</v>
       </c>
       <c r="F31" t="n">
-        <v>0.825</v>
+        <v>0.756</v>
       </c>
       <c r="G31" t="n">
-        <v>0.097</v>
+        <v>-0.039</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>-0.143</v>
       </c>
     </row>
     <row r="32">
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="E32" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="F32" t="n">
-        <v>0.742</v>
+        <v>0.732</v>
       </c>
       <c r="G32" t="n">
-        <v>0.049</v>
+        <v>0.031</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="33">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.756</v>
+        <v>0.777</v>
       </c>
       <c r="E33" t="n">
-        <v>0.834</v>
+        <v>0.887</v>
       </c>
       <c r="F33" t="n">
-        <v>0.819</v>
+        <v>0.63</v>
       </c>
       <c r="G33" t="n">
-        <v>0.063</v>
+        <v>-0.147</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.015</v>
+        <v>-0.257</v>
       </c>
     </row>
     <row r="34">
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="E34" t="n">
-        <v>0.891</v>
+        <v>0.835</v>
       </c>
       <c r="F34" t="n">
-        <v>0.799</v>
+        <v>0.71</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.018</v>
+        <v>-0.042</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.093</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="35">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.61</v>
+        <v>0.659</v>
       </c>
       <c r="E35" t="n">
-        <v>0.678</v>
+        <v>0.723</v>
       </c>
       <c r="F35" t="n">
-        <v>0.707</v>
+        <v>0.7</v>
       </c>
       <c r="G35" t="n">
-        <v>0.097</v>
+        <v>0.041</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="36">
@@ -2408,19 +2408,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.623</v>
       </c>
       <c r="E36" t="n">
-        <v>0.756</v>
+        <v>0.828</v>
       </c>
       <c r="F36" t="n">
-        <v>0.668</v>
+        <v>0.646</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.024</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.182</v>
       </c>
     </row>
     <row r="37">
@@ -2440,19 +2440,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.617</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.668</v>
+        <v>0.68</v>
       </c>
       <c r="G37" t="n">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.145</v>
+        <v>-0.131</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/appendix_e_matched_window.xlsx
+++ b/outputs/tables/appendix_e_matched_window.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.897</v>
+        <v>0.895</v>
       </c>
       <c r="D3" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.956</v>
+        <v>0.961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.898</v>
+        <v>0.896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.883</v>
+        <v>0.885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.872</v>
+        <v>0.881</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.965</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.994</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.695</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.644</v>
+        <v>0.66</v>
       </c>
       <c r="E5" t="n">
-        <v>0.643</v>
+        <v>0.577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>0.678</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>0.738</v>
       </c>
       <c r="I5" t="n">
-        <v>0.708</v>
+        <v>0.672</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.487</v>
+        <v>0.532</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.637</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.599</v>
       </c>
       <c r="J6" t="n">
-        <v>0.657</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +642,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.477</v>
+        <v>0.725</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.779</v>
+        <v>0.761</v>
       </c>
       <c r="G7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.659</v>
+        <v>0.642</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.551</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="8">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.876</v>
+        <v>0.869</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.846</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="F8" t="n">
-        <v>0.755</v>
+        <v>0.726</v>
       </c>
       <c r="G8" t="n">
-        <v>0.921</v>
+        <v>0.916</v>
       </c>
       <c r="H8" t="n">
-        <v>0.924</v>
+        <v>0.916</v>
       </c>
       <c r="I8" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.868</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.858</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.835</v>
       </c>
       <c r="D9" t="n">
-        <v>0.891</v>
+        <v>0.922</v>
       </c>
       <c r="E9" t="n">
-        <v>0.708</v>
+        <v>0.847</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.894</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911</v>
+        <v>0.86</v>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>0.894</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
-        <v>0.971</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -740,28 +740,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="D10" t="n">
-        <v>0.869</v>
+        <v>0.917</v>
       </c>
       <c r="E10" t="n">
-        <v>0.799</v>
+        <v>0.922</v>
       </c>
       <c r="F10" t="n">
-        <v>0.864</v>
+        <v>0.895</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>0.93</v>
       </c>
       <c r="H10" t="n">
-        <v>0.971</v>
+        <v>0.987</v>
       </c>
       <c r="I10" t="n">
-        <v>0.916</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.958</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="11">
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.859</v>
+        <v>0.849</v>
       </c>
       <c r="D11" t="n">
-        <v>0.797</v>
+        <v>0.804</v>
       </c>
       <c r="E11" t="n">
-        <v>0.802</v>
+        <v>0.714</v>
       </c>
       <c r="F11" t="n">
-        <v>0.741</v>
+        <v>0.747</v>
       </c>
       <c r="G11" t="n">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845</v>
+        <v>0.841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.859</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="12">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.793</v>
+        <v>0.736</v>
       </c>
       <c r="D12" t="n">
-        <v>0.946</v>
+        <v>0.902</v>
       </c>
       <c r="E12" t="n">
-        <v>0.626</v>
+        <v>0.638</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.826</v>
       </c>
       <c r="G12" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>0.856</v>
+        <v>0.862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.896</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.73</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.806</v>
+        <v>0.928</v>
       </c>
       <c r="E13" t="n">
-        <v>0.739</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.737</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.914</v>
       </c>
       <c r="I13" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="J13" t="n">
-        <v>0.899</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="14">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.854</v>
+        <v>0.885</v>
       </c>
       <c r="D14" t="n">
-        <v>0.806</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.752</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742</v>
+        <v>0.732</v>
       </c>
       <c r="G14" t="n">
-        <v>0.896</v>
+        <v>0.882</v>
       </c>
       <c r="H14" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="J14" t="n">
-        <v>0.849</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="15">
@@ -905,28 +905,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.715</v>
+        <v>0.778</v>
       </c>
       <c r="D15" t="n">
-        <v>0.834</v>
+        <v>0.868</v>
       </c>
       <c r="E15" t="n">
-        <v>0.631</v>
+        <v>0.512</v>
       </c>
       <c r="F15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.819</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.893</v>
+        <v>0.881</v>
       </c>
       <c r="J15" t="n">
-        <v>0.859</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="16">
@@ -936,28 +936,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="D16" t="n">
-        <v>0.891</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.504</v>
+        <v>0.729</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.911</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.928</v>
+        <v>0.901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.863</v>
+        <v>0.888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="17">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.829</v>
+        <v>0.767</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.783</v>
       </c>
       <c r="E17" t="n">
-        <v>0.775</v>
+        <v>0.704</v>
       </c>
       <c r="F17" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.846</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>0.843</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.789</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="18">
@@ -1003,28 +1003,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.854</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.636</v>
+        <v>0.487</v>
       </c>
       <c r="F18" t="n">
-        <v>0.668</v>
+        <v>0.647</v>
       </c>
       <c r="G18" t="n">
-        <v>0.927</v>
+        <v>0.93</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="I18" t="n">
-        <v>0.91</v>
+        <v>0.926</v>
       </c>
       <c r="J18" t="n">
-        <v>0.873</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="19">
@@ -1034,28 +1034,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="E19" t="n">
-        <v>0.539</v>
+        <v>0.571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.746</v>
       </c>
       <c r="G19" t="n">
-        <v>0.953</v>
+        <v>0.919</v>
       </c>
       <c r="H19" t="n">
-        <v>0.949</v>
+        <v>0.945</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.966</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.016</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="3">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="E3" t="n">
-        <v>0.897</v>
+        <v>0.895</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.187</v>
+        <v>0.137</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="4">
@@ -1387,16 +1387,16 @@
         <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.898</v>
+        <v>0.896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.883</v>
+        <v>0.885</v>
       </c>
       <c r="G4" t="n">
         <v>0.145</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.015</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="5">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.613</v>
+        <v>0.631</v>
       </c>
       <c r="E5" t="n">
-        <v>0.695</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643</v>
+        <v>0.577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029</v>
+        <v>-0.054</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.052</v>
+        <v>-0.115</v>
       </c>
     </row>
     <row r="6">
@@ -1448,19 +1448,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="E6" t="n">
-        <v>0.487</v>
+        <v>0.532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63</v>
+        <v>0.549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>-0.061</v>
       </c>
       <c r="H6" t="n">
-        <v>0.143</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="7">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.53</v>
+        <v>0.659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.474</v>
+        <v>0.518</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-0.141</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003</v>
+        <v>-0.207</v>
       </c>
     </row>
     <row r="8">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.745</v>
+        <v>0.757</v>
       </c>
       <c r="E8" t="n">
-        <v>0.876</v>
+        <v>0.869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06</v>
+        <v>-0.098</v>
       </c>
     </row>
     <row r="9">
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="E9" t="n">
-        <v>0.848</v>
+        <v>0.835</v>
       </c>
       <c r="F9" t="n">
-        <v>0.708</v>
+        <v>0.847</v>
       </c>
       <c r="G9" t="n">
-        <v>0.024</v>
+        <v>0.173</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="10">
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.646</v>
+        <v>0.675</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.922</v>
       </c>
       <c r="G10" t="n">
-        <v>0.154</v>
+        <v>0.247</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="11">
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.748</v>
+        <v>0.743</v>
       </c>
       <c r="E11" t="n">
-        <v>0.859</v>
+        <v>0.849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.802</v>
+        <v>0.714</v>
       </c>
       <c r="G11" t="n">
-        <v>0.054</v>
+        <v>-0.028</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.057</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="12">
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.679</v>
       </c>
       <c r="E12" t="n">
-        <v>0.793</v>
+        <v>0.736</v>
       </c>
       <c r="F12" t="n">
-        <v>0.626</v>
+        <v>0.638</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.082</v>
+        <v>-0.041</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.167</v>
+        <v>-0.098</v>
       </c>
     </row>
     <row r="13">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.677</v>
+        <v>0.654</v>
       </c>
       <c r="E13" t="n">
-        <v>0.73</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.739</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.062</v>
+        <v>-0.09</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.128</v>
       </c>
     </row>
     <row r="14">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.747</v>
+        <v>0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>0.854</v>
+        <v>0.885</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.752</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062</v>
+        <v>-0.008</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.045</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="15">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
       <c r="E15" t="n">
-        <v>0.715</v>
+        <v>0.778</v>
       </c>
       <c r="F15" t="n">
-        <v>0.631</v>
+        <v>0.512</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-0.161</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.733</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="F16" t="n">
-        <v>0.504</v>
+        <v>0.729</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.18</v>
+        <v>-0.004</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.312</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="17">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>0.698</v>
       </c>
       <c r="E17" t="n">
-        <v>0.829</v>
+        <v>0.767</v>
       </c>
       <c r="F17" t="n">
-        <v>0.775</v>
+        <v>0.704</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031</v>
+        <v>0.006</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.054</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="18">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.582</v>
+        <v>0.646</v>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.854</v>
       </c>
       <c r="F18" t="n">
-        <v>0.636</v>
+        <v>0.487</v>
       </c>
       <c r="G18" t="n">
-        <v>0.054</v>
+        <v>-0.158</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124</v>
+        <v>-0.367</v>
       </c>
     </row>
     <row r="19">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="E19" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539</v>
+        <v>0.571</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.027</v>
+        <v>0.015</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.203</v>
+        <v>-0.159</v>
       </c>
     </row>
     <row r="20">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.869</v>
+        <v>0.866</v>
       </c>
       <c r="E20" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1928,19 +1928,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.027</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="22">
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>0.902</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.872</v>
+        <v>0.881</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.03</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="23">
@@ -1992,19 +1992,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.602</v>
       </c>
       <c r="E23" t="n">
-        <v>0.644</v>
+        <v>0.66</v>
       </c>
       <c r="F23" t="n">
-        <v>0.624</v>
+        <v>0.634</v>
       </c>
       <c r="G23" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="24">
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.744</v>
+        <v>0.717</v>
       </c>
       <c r="E24" t="n">
-        <v>0.695</v>
+        <v>0.657</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.055</v>
+        <v>-0.027</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.007</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="25">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.739</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.761</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>0.068</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="26">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.727</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.846</v>
       </c>
       <c r="F26" t="n">
-        <v>0.755</v>
+        <v>0.726</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.056</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="27">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.701</v>
+        <v>0.758</v>
       </c>
       <c r="E27" t="n">
-        <v>0.891</v>
+        <v>0.922</v>
       </c>
       <c r="F27" t="n">
-        <v>0.883</v>
+        <v>0.894</v>
       </c>
       <c r="G27" t="n">
-        <v>0.182</v>
+        <v>0.136</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.028</v>
       </c>
     </row>
     <row r="28">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.789</v>
       </c>
       <c r="E28" t="n">
-        <v>0.869</v>
+        <v>0.917</v>
       </c>
       <c r="F28" t="n">
-        <v>0.864</v>
+        <v>0.895</v>
       </c>
       <c r="G28" t="n">
-        <v>0.136</v>
+        <v>0.105</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="29">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.681</v>
+        <v>0.698</v>
       </c>
       <c r="E29" t="n">
-        <v>0.797</v>
+        <v>0.804</v>
       </c>
       <c r="F29" t="n">
-        <v>0.741</v>
+        <v>0.747</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06</v>
+        <v>0.049</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.056</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="30">
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.796</v>
       </c>
       <c r="E30" t="n">
-        <v>0.946</v>
+        <v>0.902</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.826</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.106</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="31">
@@ -2248,19 +2248,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.729</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0.806</v>
+        <v>0.928</v>
       </c>
       <c r="F31" t="n">
-        <v>0.825</v>
+        <v>0.737</v>
       </c>
       <c r="G31" t="n">
-        <v>0.097</v>
+        <v>-0.078</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="32">
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.709</v>
       </c>
       <c r="E32" t="n">
-        <v>0.806</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.742</v>
+        <v>0.732</v>
       </c>
       <c r="G32" t="n">
-        <v>0.049</v>
+        <v>0.023</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.08500000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.756</v>
+        <v>0.764</v>
       </c>
       <c r="E33" t="n">
-        <v>0.834</v>
+        <v>0.868</v>
       </c>
       <c r="F33" t="n">
-        <v>0.819</v>
+        <v>0.77</v>
       </c>
       <c r="G33" t="n">
-        <v>0.063</v>
+        <v>0.006</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.015</v>
+        <v>-0.098</v>
       </c>
     </row>
     <row r="34">
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="E34" t="n">
-        <v>0.891</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.799</v>
+        <v>0.551</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.018</v>
+        <v>-0.189</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.093</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="35">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.61</v>
+        <v>0.708</v>
       </c>
       <c r="E35" t="n">
-        <v>0.678</v>
+        <v>0.783</v>
       </c>
       <c r="F35" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="G35" t="n">
-        <v>0.097</v>
+        <v>0.002</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="36">
@@ -2408,19 +2408,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="E36" t="n">
-        <v>0.756</v>
+        <v>0.761</v>
       </c>
       <c r="F36" t="n">
-        <v>0.668</v>
+        <v>0.647</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.054</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="37">
@@ -2440,19 +2440,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.639</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="F37" t="n">
-        <v>0.668</v>
+        <v>0.746</v>
       </c>
       <c r="G37" t="n">
-        <v>0.068</v>
+        <v>0.108</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.145</v>
+        <v>-0.099</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/appendix_e_matched_window.xlsx
+++ b/outputs/tables/appendix_e_matched_window.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="E2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G2" t="n">
-        <v>0.996</v>
+        <v>0.992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.995</v>
+        <v>0.994</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -513,28 +513,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.897</v>
+        <v>0.891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="E3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="I3" t="n">
-        <v>0.956</v>
+        <v>0.961</v>
       </c>
       <c r="J3" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.902</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.883</v>
+        <v>0.882</v>
       </c>
       <c r="F4" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989</v>
+        <v>0.995</v>
       </c>
       <c r="I4" t="n">
-        <v>0.965</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
-        <v>0.994</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="5">
@@ -580,28 +580,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.695</v>
+        <v>0.709</v>
       </c>
       <c r="D5" t="n">
-        <v>0.644</v>
+        <v>0.657</v>
       </c>
       <c r="E5" t="n">
-        <v>0.643</v>
+        <v>0.572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.624</v>
+        <v>0.625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717</v>
+        <v>0.756</v>
       </c>
       <c r="I5" t="n">
-        <v>0.708</v>
+        <v>0.679</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="6">
@@ -611,28 +611,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.487</v>
+        <v>0.409</v>
       </c>
       <c r="D6" t="n">
-        <v>0.695</v>
+        <v>0.756</v>
       </c>
       <c r="E6" t="n">
-        <v>0.63</v>
+        <v>0.612</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="G6" t="n">
-        <v>0.698</v>
+        <v>0.633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.599</v>
       </c>
       <c r="J6" t="n">
-        <v>0.657</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -642,28 +642,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.477</v>
+        <v>0.717</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="E7" t="n">
-        <v>0.474</v>
+        <v>0.573</v>
       </c>
       <c r="F7" t="n">
-        <v>0.779</v>
+        <v>0.591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="H7" t="n">
-        <v>0.659</v>
+        <v>0.642</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.605</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -678,28 +678,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.876</v>
+        <v>0.892</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.861</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="F8" t="n">
-        <v>0.755</v>
+        <v>0.762</v>
       </c>
       <c r="G8" t="n">
-        <v>0.921</v>
+        <v>0.918</v>
       </c>
       <c r="H8" t="n">
-        <v>0.924</v>
+        <v>0.911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.868</v>
+        <v>0.881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.858</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.848</v>
+        <v>0.793</v>
       </c>
       <c r="D9" t="n">
-        <v>0.891</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.708</v>
+        <v>0.784</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.887</v>
       </c>
       <c r="G9" t="n">
-        <v>0.911</v>
+        <v>0.875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.982</v>
+        <v>0.974</v>
       </c>
       <c r="I9" t="n">
-        <v>0.894</v>
+        <v>0.896</v>
       </c>
       <c r="J9" t="n">
-        <v>0.971</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="10">
@@ -740,28 +740,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="D10" t="n">
-        <v>0.869</v>
+        <v>0.953</v>
       </c>
       <c r="E10" t="n">
-        <v>0.799</v>
+        <v>0.845</v>
       </c>
       <c r="F10" t="n">
-        <v>0.864</v>
+        <v>0.924</v>
       </c>
       <c r="G10" t="n">
-        <v>0.953</v>
+        <v>0.954</v>
       </c>
       <c r="H10" t="n">
-        <v>0.971</v>
+        <v>0.981</v>
       </c>
       <c r="I10" t="n">
-        <v>0.916</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.958</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="11">
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.859</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>0.797</v>
+        <v>0.83</v>
       </c>
       <c r="E11" t="n">
-        <v>0.802</v>
+        <v>0.734</v>
       </c>
       <c r="F11" t="n">
-        <v>0.741</v>
+        <v>0.735</v>
       </c>
       <c r="G11" t="n">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.845</v>
+        <v>0.841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.859</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="12">
@@ -807,28 +807,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.793</v>
+        <v>0.65</v>
       </c>
       <c r="D12" t="n">
-        <v>0.946</v>
+        <v>0.887</v>
       </c>
       <c r="E12" t="n">
-        <v>0.626</v>
+        <v>0.581</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.704</v>
       </c>
       <c r="G12" t="n">
-        <v>0.917</v>
+        <v>0.923</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I12" t="n">
-        <v>0.856</v>
+        <v>0.862</v>
       </c>
       <c r="J12" t="n">
-        <v>0.896</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="13">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.73</v>
+        <v>0.677</v>
       </c>
       <c r="D13" t="n">
-        <v>0.806</v>
+        <v>0.876</v>
       </c>
       <c r="E13" t="n">
-        <v>0.739</v>
+        <v>0.694</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.823</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.924</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.914</v>
       </c>
       <c r="I13" t="n">
-        <v>0.865</v>
+        <v>0.863</v>
       </c>
       <c r="J13" t="n">
-        <v>0.899</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="14">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.854</v>
+        <v>0.872</v>
       </c>
       <c r="D14" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="F14" t="n">
-        <v>0.742</v>
+        <v>0.706</v>
       </c>
       <c r="G14" t="n">
-        <v>0.896</v>
+        <v>0.882</v>
       </c>
       <c r="H14" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="I14" t="n">
-        <v>0.841</v>
+        <v>0.845</v>
       </c>
       <c r="J14" t="n">
-        <v>0.849</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="15">
@@ -905,28 +905,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.715</v>
+        <v>0.775</v>
       </c>
       <c r="D15" t="n">
-        <v>0.834</v>
+        <v>0.829</v>
       </c>
       <c r="E15" t="n">
-        <v>0.631</v>
+        <v>0.555</v>
       </c>
       <c r="F15" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.819</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9370000000000001</v>
-      </c>
       <c r="I15" t="n">
-        <v>0.893</v>
+        <v>0.881</v>
       </c>
       <c r="J15" t="n">
-        <v>0.859</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="16">
@@ -936,28 +936,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="D16" t="n">
-        <v>0.891</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.504</v>
+        <v>0.513</v>
       </c>
       <c r="F16" t="n">
-        <v>0.799</v>
+        <v>0.796</v>
       </c>
       <c r="G16" t="n">
-        <v>0.911</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.928</v>
+        <v>0.901</v>
       </c>
       <c r="I16" t="n">
-        <v>0.863</v>
+        <v>0.888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.869</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="17">
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.829</v>
+        <v>0.823</v>
       </c>
       <c r="D17" t="n">
-        <v>0.678</v>
+        <v>0.718</v>
       </c>
       <c r="E17" t="n">
-        <v>0.775</v>
+        <v>0.738</v>
       </c>
       <c r="F17" t="n">
-        <v>0.707</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.845</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>0.845</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.789</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="18">
@@ -1003,28 +1003,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.916</v>
       </c>
       <c r="D18" t="n">
-        <v>0.756</v>
+        <v>0.843</v>
       </c>
       <c r="E18" t="n">
-        <v>0.636</v>
+        <v>0.475</v>
       </c>
       <c r="F18" t="n">
-        <v>0.668</v>
+        <v>0.731</v>
       </c>
       <c r="G18" t="n">
-        <v>0.927</v>
+        <v>0.922</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.916</v>
       </c>
       <c r="I18" t="n">
-        <v>0.91</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.873</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="19">
@@ -1034,28 +1034,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.742</v>
+        <v>0.717</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.873</v>
       </c>
       <c r="E19" t="n">
-        <v>0.539</v>
+        <v>0.61</v>
       </c>
       <c r="F19" t="n">
-        <v>0.668</v>
+        <v>0.703</v>
       </c>
       <c r="G19" t="n">
-        <v>0.953</v>
+        <v>0.927</v>
       </c>
       <c r="H19" t="n">
-        <v>0.949</v>
+        <v>0.946</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.971</v>
       </c>
     </row>
   </sheetData>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.897</v>
+        <v>0.864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.984</v>
+        <v>0.976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.968</v>
+        <v>0.953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.016</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="3">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.897</v>
+        <v>0.891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.927</v>
+        <v>0.878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.187</v>
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1387,16 +1387,16 @@
         <v>0.739</v>
       </c>
       <c r="E4" t="n">
-        <v>0.898</v>
+        <v>0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.883</v>
+        <v>0.882</v>
       </c>
       <c r="G4" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.015</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="5">
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.613</v>
+        <v>0.645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.695</v>
+        <v>0.709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.643</v>
+        <v>0.572</v>
       </c>
       <c r="G5" t="n">
-        <v>0.029</v>
+        <v>-0.073</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.052</v>
+        <v>-0.137</v>
       </c>
     </row>
     <row r="6">
@@ -1448,19 +1448,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.54</v>
+        <v>0.526</v>
       </c>
       <c r="E6" t="n">
-        <v>0.487</v>
+        <v>0.409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.63</v>
+        <v>0.612</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.143</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="7">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.53</v>
+        <v>0.653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.477</v>
+        <v>0.717</v>
       </c>
       <c r="F7" t="n">
-        <v>0.474</v>
+        <v>0.573</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.056</v>
+        <v>-0.08</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.003</v>
+        <v>-0.143</v>
       </c>
     </row>
     <row r="8">
@@ -1512,19 +1512,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.745</v>
+        <v>0.771</v>
       </c>
       <c r="E8" t="n">
-        <v>0.876</v>
+        <v>0.892</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.741</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="9">
@@ -1544,19 +1544,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.642</v>
       </c>
       <c r="E9" t="n">
-        <v>0.848</v>
+        <v>0.793</v>
       </c>
       <c r="F9" t="n">
-        <v>0.708</v>
+        <v>0.784</v>
       </c>
       <c r="G9" t="n">
-        <v>0.024</v>
+        <v>0.142</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1579,16 +1579,16 @@
         <v>0.646</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.845</v>
       </c>
       <c r="G10" t="n">
-        <v>0.154</v>
+        <v>0.199</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.014</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="11">
@@ -1608,19 +1608,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.748</v>
+        <v>0.723</v>
       </c>
       <c r="E11" t="n">
-        <v>0.859</v>
+        <v>0.82</v>
       </c>
       <c r="F11" t="n">
-        <v>0.802</v>
+        <v>0.734</v>
       </c>
       <c r="G11" t="n">
-        <v>0.054</v>
+        <v>0.011</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.057</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.708</v>
+        <v>0.622</v>
       </c>
       <c r="E12" t="n">
-        <v>0.793</v>
+        <v>0.65</v>
       </c>
       <c r="F12" t="n">
-        <v>0.626</v>
+        <v>0.581</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.082</v>
+        <v>-0.041</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.167</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.677</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.73</v>
-      </c>
       <c r="F13" t="n">
-        <v>0.739</v>
+        <v>0.694</v>
       </c>
       <c r="G13" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
       <c r="H13" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="E14" t="n">
-        <v>0.854</v>
+        <v>0.872</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062</v>
+        <v>-0.013</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.045</v>
+        <v>-0.134</v>
       </c>
     </row>
     <row r="15">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.657</v>
+        <v>0.671</v>
       </c>
       <c r="E15" t="n">
-        <v>0.715</v>
+        <v>0.775</v>
       </c>
       <c r="F15" t="n">
-        <v>0.631</v>
+        <v>0.555</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.026</v>
+        <v>-0.116</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="16">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.707</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="F16" t="n">
-        <v>0.504</v>
+        <v>0.513</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.18</v>
+        <v>-0.194</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.312</v>
+        <v>-0.287</v>
       </c>
     </row>
     <row r="17">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.744</v>
+        <v>0.719</v>
       </c>
       <c r="E17" t="n">
-        <v>0.829</v>
+        <v>0.823</v>
       </c>
       <c r="F17" t="n">
-        <v>0.775</v>
+        <v>0.738</v>
       </c>
       <c r="G17" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.054</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1832,19 +1832,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.582</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.916</v>
       </c>
       <c r="F18" t="n">
-        <v>0.636</v>
+        <v>0.475</v>
       </c>
       <c r="G18" t="n">
-        <v>0.054</v>
+        <v>-0.216</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.124</v>
+        <v>-0.441</v>
       </c>
     </row>
     <row r="19">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.742</v>
+        <v>0.717</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539</v>
+        <v>0.61</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.027</v>
+        <v>0.051</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.203</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="20">
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.869</v>
+        <v>0.866</v>
       </c>
       <c r="E20" t="n">
-        <v>0.968</v>
+        <v>0.977</v>
       </c>
       <c r="F20" t="n">
-        <v>0.969</v>
+        <v>0.957</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21">
@@ -1928,19 +1928,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="E21" t="n">
-        <v>0.91</v>
+        <v>0.931</v>
       </c>
       <c r="F21" t="n">
-        <v>0.884</v>
+        <v>0.895</v>
       </c>
       <c r="G21" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.027</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="22">
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="E22" t="n">
-        <v>0.902</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.872</v>
+        <v>0.882</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136</v>
+        <v>0.115</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.03</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="23">
@@ -1992,19 +1992,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.598</v>
       </c>
       <c r="E23" t="n">
-        <v>0.644</v>
+        <v>0.657</v>
       </c>
       <c r="F23" t="n">
-        <v>0.624</v>
+        <v>0.625</v>
       </c>
       <c r="G23" t="n">
-        <v>0.015</v>
+        <v>0.027</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="24">
@@ -2024,19 +2024,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.744</v>
+        <v>0.783</v>
       </c>
       <c r="E24" t="n">
-        <v>0.695</v>
+        <v>0.756</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.055</v>
+        <v>-0.022</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="25">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.739</v>
+        <v>0.787</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.591</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04</v>
+        <v>-0.195</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.169</v>
       </c>
     </row>
     <row r="26">
@@ -2088,19 +2088,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.734</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.861</v>
       </c>
       <c r="F26" t="n">
-        <v>0.755</v>
+        <v>0.762</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.056</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="27">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.701</v>
+        <v>0.776</v>
       </c>
       <c r="E27" t="n">
-        <v>0.891</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.883</v>
+        <v>0.887</v>
       </c>
       <c r="G27" t="n">
-        <v>0.182</v>
+        <v>0.112</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.053</v>
       </c>
     </row>
     <row r="28">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.727</v>
+        <v>0.794</v>
       </c>
       <c r="E28" t="n">
-        <v>0.869</v>
+        <v>0.953</v>
       </c>
       <c r="F28" t="n">
-        <v>0.864</v>
+        <v>0.924</v>
       </c>
       <c r="G28" t="n">
-        <v>0.136</v>
+        <v>0.13</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="29">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.681</v>
+        <v>0.716</v>
       </c>
       <c r="E29" t="n">
-        <v>0.797</v>
+        <v>0.83</v>
       </c>
       <c r="F29" t="n">
-        <v>0.741</v>
+        <v>0.735</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06</v>
+        <v>0.019</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.056</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="30">
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.786</v>
       </c>
       <c r="E30" t="n">
-        <v>0.946</v>
+        <v>0.887</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.704</v>
       </c>
       <c r="G30" t="n">
-        <v>0.022</v>
+        <v>-0.082</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.106</v>
+        <v>-0.183</v>
       </c>
     </row>
     <row r="31">
@@ -2248,19 +2248,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.729</v>
+        <v>0.78</v>
       </c>
       <c r="E31" t="n">
-        <v>0.806</v>
+        <v>0.876</v>
       </c>
       <c r="F31" t="n">
-        <v>0.825</v>
+        <v>0.823</v>
       </c>
       <c r="G31" t="n">
-        <v>0.097</v>
+        <v>0.043</v>
       </c>
       <c r="H31" t="n">
-        <v>0.02</v>
+        <v>-0.053</v>
       </c>
     </row>
     <row r="32">
@@ -2280,19 +2280,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="E32" t="n">
-        <v>0.806</v>
+        <v>0.805</v>
       </c>
       <c r="F32" t="n">
-        <v>0.742</v>
+        <v>0.706</v>
       </c>
       <c r="G32" t="n">
-        <v>0.049</v>
+        <v>0.005</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="33">
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.756</v>
+        <v>0.738</v>
       </c>
       <c r="E33" t="n">
-        <v>0.834</v>
+        <v>0.829</v>
       </c>
       <c r="F33" t="n">
-        <v>0.819</v>
+        <v>0.738</v>
       </c>
       <c r="G33" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.015</v>
+        <v>-0.091</v>
       </c>
     </row>
     <row r="34">
@@ -2344,19 +2344,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.739</v>
       </c>
       <c r="E34" t="n">
-        <v>0.891</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.799</v>
+        <v>0.796</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.018</v>
+        <v>0.057</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.093</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="35">
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.61</v>
+        <v>0.643</v>
       </c>
       <c r="E35" t="n">
-        <v>0.678</v>
+        <v>0.718</v>
       </c>
       <c r="F35" t="n">
-        <v>0.707</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="36">
@@ -2408,19 +2408,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="E36" t="n">
-        <v>0.756</v>
+        <v>0.843</v>
       </c>
       <c r="F36" t="n">
-        <v>0.668</v>
+        <v>0.731</v>
       </c>
       <c r="G36" t="n">
-        <v>0.109</v>
+        <v>0.081</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.112</v>
       </c>
     </row>
     <row r="37">
@@ -2440,19 +2440,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.6</v>
+        <v>0.664</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.873</v>
       </c>
       <c r="F37" t="n">
-        <v>0.668</v>
+        <v>0.703</v>
       </c>
       <c r="G37" t="n">
-        <v>0.068</v>
+        <v>0.04</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.145</v>
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
